--- a/data/privx_ct.xlsx
+++ b/data/privx_ct.xlsx
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C102" t="n">

--- a/data/privx_ct.xlsx
+++ b/data/privx_ct.xlsx
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C102" t="n">

--- a/data/privx_ct.xlsx
+++ b/data/privx_ct.xlsx
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C102" t="n">
